--- a/r5-aist-trustworthyai-poc-pipeline/ValueSet-ehds-data-category-vs.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/ValueSet-ehds-data-category-vs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EHDS Data Category ValueSet (Final Regulation 2025/327)</t>
+    <t>EHDS Data Category ValueSet</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mandatory categories of electronic health data for secondary use according to Art. 51 EHDS.</t>
+    <t>Categories of electronic health data relevant for secondary-use documentation under the EHDS (EHDS Art. 51).</t>
   </si>
   <si>
     <t>Purpose</t>
